--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_MACCABI RAPYD TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_MACCABI RAPYD TEL AVIV.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA54"/>
+  <dimension ref="A1:BA52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,16 +671,16 @@
         <v>0.2676550916894265</v>
       </c>
       <c r="J2" t="n">
-        <v>423</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>527</v>
+        <v>19</v>
       </c>
       <c r="L2" t="n">
-        <v>330</v>
+        <v>20</v>
       </c>
       <c r="M2" t="n">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N2" t="n">
         <v>1162</v>
@@ -752,13 +752,13 @@
         <v>1.058986175115207</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.8703703703703703</v>
+        <v>0.03497942386831276</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.073319755600815</v>
+        <v>0.03869653767820774</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.701030927835051</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
         <v>1.624463519313305</v>
@@ -801,16 +801,16 @@
         <v>0.2676550916894265</v>
       </c>
       <c r="J3" t="n">
-        <v>11.13157894736842</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="K3" t="n">
-        <v>13.86842105263158</v>
+        <v>0.5</v>
       </c>
       <c r="L3" t="n">
-        <v>8.684210526315789</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="M3" t="n">
-        <v>11.21052631578947</v>
+        <v>11.26315789473684</v>
       </c>
       <c r="N3" t="n">
         <v>30.57894736842105</v>
@@ -882,13 +882,13 @@
         <v>1.058986175115207</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.8703703703703705</v>
+        <v>0.03497942386831276</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.073319755600815</v>
+        <v>0.03869653767820774</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.701030927835051</v>
+        <v>2</v>
       </c>
       <c r="AN3" t="n">
         <v>1.624463519313305</v>
@@ -931,13 +931,13 @@
         <v>0.2598019801980198</v>
       </c>
       <c r="J4" t="n">
-        <v>401</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>488</v>
+        <v>16</v>
       </c>
       <c r="L4" t="n">
-        <v>372</v>
+        <v>17</v>
       </c>
       <c r="M4" t="n">
         <v>450</v>
@@ -1012,13 +1012,13 @@
         <v>1.060552092609083</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8605150214592274</v>
+        <v>0.03218884120171674</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.053995680345572</v>
+        <v>0.03455723542116631</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.706422018348624</v>
+        <v>2.125</v>
       </c>
       <c r="AN4" t="n">
         <v>1.683127572016461</v>
@@ -1061,13 +1061,13 @@
         <v>0.2598019801980198</v>
       </c>
       <c r="J5" t="n">
-        <v>10.55263157894737</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="K5" t="n">
-        <v>12.8421052631579</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="L5" t="n">
-        <v>9.789473684210526</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="M5" t="n">
         <v>11.8421052631579</v>
@@ -1142,13 +1142,13 @@
         <v>1.060552092609083</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8605150214592274</v>
+        <v>0.03218884120171674</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.053995680345572</v>
+        <v>0.0345572354211663</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.706422018348624</v>
+        <v>2.125</v>
       </c>
       <c r="AN5" t="n">
         <v>1.683127572016461</v>
@@ -1486,16 +1486,16 @@
         <v>207</v>
       </c>
       <c r="U8" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>46</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>750:47</t>
+          <t>390:12</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>6.893</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.109</v>
+        <v>0.21</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.014</v>
+        <v>0.028</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.034</v>
+        <v>0.065</v>
       </c>
       <c r="BA8" t="n">
         <v>0.052</v>
@@ -1651,16 +1651,16 @@
         <v>603</v>
       </c>
       <c r="U9" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>193</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>1791:34</t>
+          <t>1009:23</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>8.711</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.094</v>
+        <v>0.166</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.047</v>
+        <v>0.083</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.109</v>
+        <v>0.193</v>
       </c>
       <c r="BA9" t="n">
         <v>0.044</v>
@@ -1816,16 +1816,16 @@
         <v>338</v>
       </c>
       <c r="U10" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="V10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="X10" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="n">
         <v>98</v>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>1479:27</t>
+          <t>730:37</t>
         </is>
       </c>
       <c r="AO10" t="n">
@@ -1905,13 +1905,13 @@
         <v>6.36</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.127</v>
+        <v>0.257</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.015</v>
+        <v>0.031</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.036</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="BA10" t="n">
         <v>0.152</v>
@@ -1969,7 +1969,7 @@
         <v>38</v>
       </c>
       <c r="Q11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R11" t="n">
         <v>105</v>
@@ -1981,16 +1981,16 @@
         <v>243</v>
       </c>
       <c r="U11" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
         <v>112</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1139:56</t>
+          <t>520:26</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>4.632</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.093</v>
+        <v>0.203</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.025</v>
+        <v>0.054</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.034</v>
+        <v>0.075</v>
       </c>
       <c r="BA11" t="n">
         <v>0.022</v>
@@ -2146,16 +2146,16 @@
         <v>58</v>
       </c>
       <c r="U12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>20</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>335:59</t>
+          <t>161:11</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>3.417</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.149</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.029</v>
+        <v>0.06</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.055</v>
+        <v>0.114</v>
       </c>
       <c r="BA12" t="n">
         <v>0.003</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,7 +2730,7 @@
         <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.068</v>
+        <v>0.285</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>46</v>
       </c>
       <c r="Q16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R16" t="n">
         <v>45</v>
@@ -2806,16 +2806,16 @@
         <v>380</v>
       </c>
       <c r="U16" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="n">
         <v>127</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>1242:15</t>
+          <t>635:43</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>8.542999999999999</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.157</v>
+        <v>0.306</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.006</v>
+        <v>0.012</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.059</v>
+        <v>0.116</v>
       </c>
       <c r="BA16" t="n">
         <v>0.06</v>
@@ -2971,16 +2971,16 @@
         <v>588</v>
       </c>
       <c r="U17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>200</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>1540:52</t>
+          <t>870:27</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>10.227</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.139</v>
+        <v>0.246</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.045</v>
+        <v>0.079</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.126</v>
       </c>
       <c r="BA17" t="n">
         <v>0.067</v>
@@ -3136,16 +3136,16 @@
         <v>388</v>
       </c>
       <c r="U18" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="V18" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="X18" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>128</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>1647:05</t>
+          <t>885:11</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,13 +3225,13 @@
         <v>8.061999999999999</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.042</v>
+        <v>0.078</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="BA18" t="n">
         <v>0.027</v>
@@ -3301,16 +3301,16 @@
         <v>125</v>
       </c>
       <c r="U19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
         <v>43</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>1096:20</t>
+          <t>453:59</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>13.714</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.048</v>
+        <v>0.115</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.032</v>
+        <v>0.078</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.048</v>
+        <v>0.117</v>
       </c>
       <c r="BA19" t="n">
         <v>0.008999999999999999</v>
@@ -3466,16 +3466,16 @@
         <v>121</v>
       </c>
       <c r="U20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>844:37</t>
+          <t>385:54</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,13 +3555,13 @@
         <v>11.889</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.054</v>
+        <v>0.118</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.026</v>
+        <v>0.056</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.041</v>
+        <v>0.089</v>
       </c>
       <c r="BA20" t="n">
         <v>0.022</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>36:06</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AO22" t="n">
@@ -3885,13 +3885,13 @@
         <v>2</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.048</v>
+        <v>0.109</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.12</v>
+        <v>0.268</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.032</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3961,16 +3961,16 @@
         <v>141</v>
       </c>
       <c r="U23" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>32</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>677:33</t>
+          <t>326:48</t>
         </is>
       </c>
       <c r="AO23" t="n">
@@ -4050,13 +4050,13 @@
         <v>10.176</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.106</v>
+        <v>0.22</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.006</v>
+        <v>0.013</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.027</v>
+        <v>0.056</v>
       </c>
       <c r="BA23" t="n">
         <v>0.041</v>
@@ -4126,16 +4126,16 @@
         <v>307</v>
       </c>
       <c r="U24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="W24" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>94</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>978:43</t>
+          <t>436:55</t>
         </is>
       </c>
       <c r="AO24" t="n">
@@ -4215,13 +4215,13 @@
         <v>15.273</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.08</v>
+        <v>0.179</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.052</v>
+        <v>0.116</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.076</v>
+        <v>0.171</v>
       </c>
       <c r="BA24" t="n">
         <v>0.024</v>
@@ -4291,10 +4291,10 @@
         <v>54</v>
       </c>
       <c r="U25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>203:10</t>
+          <t>103:01</t>
         </is>
       </c>
       <c r="AO25" t="n">
@@ -4380,13 +4380,13 @@
         <v>6</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.078</v>
+        <v>0.153</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.136</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.057</v>
+        <v>0.112</v>
       </c>
       <c r="BA25" t="n">
         <v>0.003</v>
@@ -4456,16 +4456,16 @@
         <v>344</v>
       </c>
       <c r="U26" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="X26" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
         <v>27</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>1562:47</t>
+          <t>738:20</t>
         </is>
       </c>
       <c r="AO26" t="n">
@@ -4545,13 +4545,13 @@
         <v>4.895</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.094</v>
+        <v>0.198</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.008</v>
+        <v>0.016</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.043</v>
+        <v>0.092</v>
       </c>
       <c r="BA26" t="n">
         <v>0.181</v>
@@ -4725,163 +4725,163 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>38</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>3425</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>795</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1478</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1085</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>857</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>871</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>258</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="T28" t="n">
-        <v>140</v>
+        <v>4042</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1162</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1414</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>0.822</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>257</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>596</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>0.431</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>0.403</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>351</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1018</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>7675:00</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>17</v>
+        <v>3406.08</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>0.534</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.582</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.006</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.624</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>7.124</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="BA28" t="n">
         <v>0</v>
@@ -4890,44 +4890,44 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>38</v>
       </c>
       <c r="C29" t="n">
-        <v>3425</v>
+        <v>3521</v>
       </c>
       <c r="D29" t="n">
-        <v>795</v>
+        <v>837</v>
       </c>
       <c r="E29" t="n">
-        <v>1478</v>
+        <v>1402</v>
       </c>
       <c r="F29" t="n">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="G29" t="n">
-        <v>1085</v>
+        <v>1123</v>
       </c>
       <c r="H29" t="n">
-        <v>686</v>
+        <v>656</v>
       </c>
       <c r="I29" t="n">
-        <v>857</v>
+        <v>830</v>
       </c>
       <c r="J29" t="n">
-        <v>757</v>
+        <v>818</v>
       </c>
       <c r="K29" t="n">
-        <v>871</v>
+        <v>931</v>
       </c>
       <c r="L29" t="n">
-        <v>491</v>
+        <v>463</v>
       </c>
       <c r="M29" t="n">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="N29" t="n">
         <v>172</v>
@@ -4936,76 +4936,76 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="Q29" t="n">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="R29" t="n">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="S29" t="n">
-        <v>834</v>
+        <v>814</v>
       </c>
       <c r="T29" t="n">
-        <v>4042</v>
+        <v>4261</v>
       </c>
       <c r="U29" t="n">
-        <v>423</v>
+        <v>15</v>
       </c>
       <c r="V29" t="n">
-        <v>527</v>
+        <v>16</v>
       </c>
       <c r="W29" t="n">
-        <v>330</v>
+        <v>17</v>
       </c>
       <c r="X29" t="n">
-        <v>194</v>
+        <v>8</v>
       </c>
       <c r="Y29" t="n">
-        <v>1162</v>
+        <v>1139</v>
       </c>
       <c r="Z29" t="n">
-        <v>1414</v>
+        <v>1328</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.822</v>
+        <v>0.858</v>
       </c>
       <c r="AB29" t="n">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="AC29" t="n">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.431</v>
+        <v>0.499</v>
       </c>
       <c r="AE29" t="n">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="AF29" t="n">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="AG29" t="n">
-        <v>0.403</v>
+        <v>0.415</v>
       </c>
       <c r="AH29" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="AI29" t="n">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.478</v>
+        <v>0.379</v>
       </c>
       <c r="AK29" t="n">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="AL29" t="n">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.345</v>
+        <v>0.351</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5013,31 +5013,31 @@
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>3406.08</v>
+        <v>3376.2</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.534</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.582</v>
+        <v>0.609</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.006</v>
+        <v>1.043</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.137</v>
+        <v>0.144</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.268</v>
+        <v>0.26</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.624</v>
+        <v>1.683</v>
       </c>
       <c r="AV29" t="n">
-        <v>5.5</v>
+        <v>5.195</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.124</v>
+        <v>6.879</v>
       </c>
       <c r="AX29" t="n">
         <v>0.2</v>
@@ -5055,1144 +5055,1144 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>38</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3521</v>
-      </c>
-      <c r="D30" t="n">
-        <v>837</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1402</v>
-      </c>
-      <c r="F30" t="n">
-        <v>397</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1123</v>
-      </c>
-      <c r="H30" t="n">
-        <v>656</v>
-      </c>
-      <c r="I30" t="n">
-        <v>830</v>
-      </c>
-      <c r="J30" t="n">
-        <v>818</v>
-      </c>
-      <c r="K30" t="n">
-        <v>931</v>
-      </c>
-      <c r="L30" t="n">
-        <v>463</v>
-      </c>
-      <c r="M30" t="n">
-        <v>236</v>
-      </c>
-      <c r="N30" t="n">
-        <v>172</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>486</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>450</v>
-      </c>
-      <c r="R30" t="n">
-        <v>743</v>
-      </c>
-      <c r="S30" t="n">
-        <v>814</v>
-      </c>
-      <c r="T30" t="n">
-        <v>4261</v>
-      </c>
-      <c r="U30" t="n">
-        <v>401</v>
-      </c>
-      <c r="V30" t="n">
-        <v>488</v>
-      </c>
-      <c r="W30" t="n">
-        <v>372</v>
-      </c>
-      <c r="X30" t="n">
-        <v>218</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1139</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1328</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>303</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>607</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>51</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>123</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>39</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>103</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>358</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1020</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>7675:00</t>
-        </is>
-      </c>
-      <c r="AO30" t="n">
-        <v>3376.2</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.043</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.683</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>5.195</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>6.879</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="inlineStr"/>
+          <t>#0 I. LUNDBERG (Per Game)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4.438</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.312</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.688</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.625</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="T31" t="n">
+        <v>207</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.188</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>4.062</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>24:23</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4.821</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>6.893</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0.132</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#0 I. LUNDBERG (Per Game)</t>
+          <t>#1 J. HOARD (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>11.417</v>
       </c>
       <c r="D32" t="n">
-        <v>2.188</v>
+        <v>3.806</v>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>6.667</v>
       </c>
       <c r="F32" t="n">
-        <v>1.438</v>
+        <v>0.389</v>
       </c>
       <c r="G32" t="n">
-        <v>4.438</v>
+        <v>1.278</v>
       </c>
       <c r="H32" t="n">
-        <v>2.312</v>
+        <v>2.639</v>
       </c>
       <c r="I32" t="n">
-        <v>2.688</v>
+        <v>3.056</v>
       </c>
       <c r="J32" t="n">
-        <v>3.625</v>
+        <v>1.25</v>
       </c>
       <c r="K32" t="n">
-        <v>1.375</v>
+        <v>4.694</v>
       </c>
       <c r="L32" t="n">
-        <v>0.625</v>
+        <v>2.167</v>
       </c>
       <c r="M32" t="n">
-        <v>0.75</v>
+        <v>0.806</v>
       </c>
       <c r="N32" t="n">
-        <v>0.312</v>
+        <v>0.694</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.75</v>
+        <v>1.056</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.625</v>
+        <v>1.028</v>
       </c>
       <c r="R32" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.472</v>
       </c>
       <c r="S32" t="n">
-        <v>3.125</v>
+        <v>2.417</v>
       </c>
       <c r="T32" t="n">
-        <v>207</v>
+        <v>603</v>
       </c>
       <c r="U32" t="n">
-        <v>2.562</v>
+        <v>0.056</v>
       </c>
       <c r="V32" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.9379999999999999</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.875</v>
+        <v>5.361</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.125</v>
+        <v>6.611</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.92</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.25</v>
+        <v>0.778</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.188</v>
+        <v>2.167</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.571</v>
+        <v>0.359</v>
       </c>
       <c r="AE32" t="n">
-        <v>0.375</v>
+        <v>0.306</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>0.528</v>
       </c>
       <c r="AG32" t="n">
-        <v>0.375</v>
+        <v>0.579</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.125</v>
+        <v>0.083</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.375</v>
+        <v>0.167</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.312</v>
+        <v>0.306</v>
       </c>
       <c r="AL32" t="n">
-        <v>4.062</v>
+        <v>1.111</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.323</v>
+        <v>0.275</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>46:55</t>
+          <t>28:02</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>11.37</v>
+        <v>10.344</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.515</v>
+        <v>0.552</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.572</v>
+        <v>0.615</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.967</v>
+        <v>1.104</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.154</v>
+        <v>0.102</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.274</v>
+        <v>0.332</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.071</v>
+        <v>1.184</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.821</v>
+        <v>7.526</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.893</v>
+        <v>8.711</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.109</v>
+        <v>0.166</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.014</v>
+        <v>0.083</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.034</v>
+        <v>0.193</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.132</v>
+        <v>0.047</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#1 J. HOARD (Per Game)</t>
+          <t>#2 J. CLARK III (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C33" t="n">
-        <v>11.417</v>
+        <v>9.513999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>3.806</v>
+        <v>2.378</v>
       </c>
       <c r="E33" t="n">
-        <v>6.667</v>
+        <v>4.73</v>
       </c>
       <c r="F33" t="n">
-        <v>0.389</v>
+        <v>1.189</v>
       </c>
       <c r="G33" t="n">
-        <v>1.278</v>
+        <v>3.865</v>
       </c>
       <c r="H33" t="n">
-        <v>2.639</v>
+        <v>1.189</v>
       </c>
       <c r="I33" t="n">
-        <v>3.056</v>
+        <v>1.486</v>
       </c>
       <c r="J33" t="n">
-        <v>1.25</v>
+        <v>4.297</v>
       </c>
       <c r="K33" t="n">
-        <v>4.694</v>
+        <v>1.243</v>
       </c>
       <c r="L33" t="n">
-        <v>2.167</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>0.806</v>
+        <v>1.297</v>
       </c>
       <c r="N33" t="n">
-        <v>0.694</v>
+        <v>0.297</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.056</v>
+        <v>2.027</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.028</v>
+        <v>1.946</v>
       </c>
       <c r="R33" t="n">
-        <v>1.472</v>
+        <v>2.405</v>
       </c>
       <c r="S33" t="n">
-        <v>2.417</v>
+        <v>1.676</v>
       </c>
       <c r="T33" t="n">
-        <v>603</v>
+        <v>338</v>
       </c>
       <c r="U33" t="n">
-        <v>1.583</v>
+        <v>0.108</v>
       </c>
       <c r="V33" t="n">
-        <v>1.917</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0.806</v>
+        <v>0.135</v>
       </c>
       <c r="X33" t="n">
-        <v>0.5</v>
+        <v>0.054</v>
       </c>
       <c r="Y33" t="n">
-        <v>5.361</v>
+        <v>2.649</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.611</v>
+        <v>3.432</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.772</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.778</v>
+        <v>0.784</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.167</v>
+        <v>1.919</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.359</v>
+        <v>0.408</v>
       </c>
       <c r="AE33" t="n">
-        <v>0.306</v>
+        <v>0.135</v>
       </c>
       <c r="AF33" t="n">
-        <v>0.528</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AG33" t="n">
-        <v>0.579</v>
+        <v>0.238</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.083</v>
+        <v>0.027</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.167</v>
+        <v>0.081</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.306</v>
+        <v>1.162</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.111</v>
+        <v>3.784</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.275</v>
+        <v>0.307</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>49:45</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>10.344</v>
+        <v>11.276</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.552</v>
+        <v>0.484</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.615</v>
+        <v>0.514</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.104</v>
+        <v>0.844</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.102</v>
+        <v>0.18</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.332</v>
+        <v>0.138</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.184</v>
+        <v>2.12</v>
       </c>
       <c r="AV33" t="n">
-        <v>7.526</v>
+        <v>4.24</v>
       </c>
       <c r="AW33" t="n">
-        <v>8.711</v>
+        <v>6.36</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.094</v>
+        <v>0.257</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.047</v>
+        <v>0.031</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.109</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.047</v>
+        <v>0.157</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#2 J. CLARK III (Per Game)</t>
+          <t>#3 M. SANTOS (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C34" t="n">
-        <v>9.513999999999999</v>
+        <v>6.737</v>
       </c>
       <c r="D34" t="n">
-        <v>2.378</v>
+        <v>1.342</v>
       </c>
       <c r="E34" t="n">
-        <v>4.73</v>
+        <v>2.421</v>
       </c>
       <c r="F34" t="n">
-        <v>1.189</v>
+        <v>0.632</v>
       </c>
       <c r="G34" t="n">
-        <v>3.865</v>
+        <v>1.579</v>
       </c>
       <c r="H34" t="n">
-        <v>1.189</v>
+        <v>2.158</v>
       </c>
       <c r="I34" t="n">
-        <v>1.486</v>
+        <v>2.684</v>
       </c>
       <c r="J34" t="n">
-        <v>4.297</v>
+        <v>0.632</v>
       </c>
       <c r="K34" t="n">
-        <v>1.243</v>
+        <v>0.895</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>1.297</v>
+        <v>0.553</v>
       </c>
       <c r="N34" t="n">
-        <v>0.297</v>
+        <v>0.447</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.027</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.946</v>
+        <v>0.947</v>
       </c>
       <c r="R34" t="n">
-        <v>2.405</v>
+        <v>2.763</v>
       </c>
       <c r="S34" t="n">
-        <v>1.676</v>
+        <v>2.763</v>
       </c>
       <c r="T34" t="n">
-        <v>338</v>
+        <v>243</v>
       </c>
       <c r="U34" t="n">
-        <v>1.703</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.649</v>
+        <v>0.053</v>
       </c>
       <c r="W34" t="n">
-        <v>1.27</v>
+        <v>0.053</v>
       </c>
       <c r="X34" t="n">
-        <v>0.73</v>
+        <v>0.053</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.649</v>
+        <v>2.947</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.432</v>
+        <v>3.368</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.772</v>
+        <v>0.875</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.784</v>
+        <v>0.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.919</v>
+        <v>1.053</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.408</v>
+        <v>0.475</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.135</v>
+        <v>0.053</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.158</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.238</v>
+        <v>0.333</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.081</v>
+        <v>0.026</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.162</v>
+        <v>0.632</v>
       </c>
       <c r="AL34" t="n">
-        <v>3.784</v>
+        <v>1.553</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.307</v>
+        <v>0.407</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>39:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>11.276</v>
+        <v>6.181</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.484</v>
+        <v>0.572</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.514</v>
+        <v>0.65</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.844</v>
+        <v>1.09</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.18</v>
+        <v>0.162</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.138</v>
+        <v>0.539</v>
       </c>
       <c r="AU34" t="n">
-        <v>2.12</v>
+        <v>0.632</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.36</v>
+        <v>4.632</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.127</v>
+        <v>0.203</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.015</v>
+        <v>0.054</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.036</v>
+        <v>0.075</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.157</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#3 M. SANTOS (Per Game)</t>
+          <t>#4 L. GUR (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>6.737</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>1.342</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>2.421</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>1.579</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>2.158</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2.684</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0.632</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>0.895</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6840000000000001</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0.553</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0.447</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
         <v>1</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0.921</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.763</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.763</v>
-      </c>
-      <c r="T35" t="n">
-        <v>243</v>
-      </c>
       <c r="U35" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.184</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>0.658</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2.947</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>3.368</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.053</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.475</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.553</v>
+        <v>1</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.407</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>29:59</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>6.181</v>
+        <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.572</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.65</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.539</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.632</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.632</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.093</v>
+        <v>0.059</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.034</v>
+        <v>0.151</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.022</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#4 L. GUR (Per Game)</t>
+          <t>#4 G. LAVI (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>23</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.174</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="T36" t="n">
+        <v>58</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>1</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AL36" t="n">
-        <v>1</v>
+        <v>0.348</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>1</v>
+        <v>2.322</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>0.713</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>0.216</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>3.083</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>3.417</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.059</v>
+        <v>0.149</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.151</v>
+        <v>0.114</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.032</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#4 G. LAVI (Per Game)</t>
+          <t>#5 A. EBO (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>2.565</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.783</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.478</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.348</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.696</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.522</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.522</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0.957</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.478</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0.348</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.087</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -6204,91 +6204,91 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.348</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>2.322</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.6889999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.713</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.105</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.225</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.216</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>3.083</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>3.417</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.07199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#5 A. EBO (Per Game)</t>
+          <t>#6 U. TRIFUNOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -6327,7 +6327,7 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -6351,13 +6351,13 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -6381,27 +6381,27 @@
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AM38" t="n">
         <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:35</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS38" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
         <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>0.285</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -6434,869 +6434,869 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#6 U. TRIFUNOVIC (Per Game)</t>
+          <t>#8 L. WALKER IV (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="C39" t="n">
+        <v>14.655</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.138</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.345</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.345</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.414</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.172</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.207</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.586</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.517</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.552</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.586</v>
+      </c>
+      <c r="T39" t="n">
+        <v>380</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>4.379</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>5.276</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.759</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AF39" t="n">
         <v>1</v>
       </c>
-      <c r="D39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
+      <c r="AG39" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>1</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.207</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.5</v>
+        <v>6.552</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.337</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>1</v>
+        <v>14.908</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.5</v>
+        <v>0.497</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="AR39" t="n">
-        <v>1</v>
+        <v>0.983</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>0.294</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>7.174</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>8.542999999999999</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.068</v>
+        <v>0.306</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#8 L. WALKER IV (Per Game)</t>
+          <t>#9 R. SORKIN (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C40" t="n">
-        <v>14.655</v>
+        <v>13.5</v>
       </c>
       <c r="D40" t="n">
-        <v>2.138</v>
+        <v>4.395</v>
       </c>
       <c r="E40" t="n">
-        <v>4.69</v>
+        <v>7.711</v>
       </c>
       <c r="F40" t="n">
-        <v>2.345</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>6.69</v>
+        <v>2.395</v>
       </c>
       <c r="H40" t="n">
-        <v>3.345</v>
+        <v>2.263</v>
       </c>
       <c r="I40" t="n">
-        <v>4.414</v>
+        <v>2.763</v>
       </c>
       <c r="J40" t="n">
-        <v>2.172</v>
+        <v>1.737</v>
       </c>
       <c r="K40" t="n">
-        <v>2.207</v>
+        <v>2.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0.241</v>
+        <v>1.684</v>
       </c>
       <c r="M40" t="n">
-        <v>0.793</v>
+        <v>0.579</v>
       </c>
       <c r="N40" t="n">
-        <v>0.552</v>
+        <v>1.158</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.586</v>
+        <v>1.158</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.483</v>
+        <v>1.105</v>
       </c>
       <c r="R40" t="n">
-        <v>1.552</v>
+        <v>1.895</v>
       </c>
       <c r="S40" t="n">
-        <v>3.586</v>
+        <v>2.763</v>
       </c>
       <c r="T40" t="n">
-        <v>380</v>
+        <v>588</v>
       </c>
       <c r="U40" t="n">
-        <v>1.759</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.276</v>
+        <v>0.053</v>
       </c>
       <c r="W40" t="n">
-        <v>2.31</v>
+        <v>0.053</v>
       </c>
       <c r="X40" t="n">
-        <v>1.172</v>
+        <v>0.026</v>
       </c>
       <c r="Y40" t="n">
-        <v>4.379</v>
+        <v>5.263</v>
       </c>
       <c r="Z40" t="n">
-        <v>5.276</v>
+        <v>6.842</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.83</v>
+        <v>0.769</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.263</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.759</v>
+        <v>2.816</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.392</v>
+        <v>0.449</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.414</v>
+        <v>0.132</v>
       </c>
       <c r="AF40" t="n">
-        <v>1</v>
+        <v>0.316</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.414</v>
+        <v>0.417</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.138</v>
+        <v>0.026</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.138</v>
+        <v>0.079</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="AK40" t="n">
-        <v>2.207</v>
+        <v>0.789</v>
       </c>
       <c r="AL40" t="n">
-        <v>6.552</v>
+        <v>2.316</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.337</v>
+        <v>0.341</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>42:50</t>
+          <t>22:54</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>14.908</v>
+        <v>12.479</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.497</v>
+        <v>0.556</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.55</v>
+        <v>0.596</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.983</v>
+        <v>1.082</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.106</v>
+        <v>0.093</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.294</v>
+        <v>0.224</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>7.174</v>
+        <v>8.727</v>
       </c>
       <c r="AW40" t="n">
-        <v>8.542999999999999</v>
+        <v>10.227</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.157</v>
+        <v>0.246</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.006</v>
+        <v>0.079</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.059</v>
+        <v>0.126</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.082</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#9 R. SORKIN (Per Game)</t>
+          <t>#10 O. BRISSETT (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C41" t="n">
-        <v>13.5</v>
+        <v>8.722</v>
       </c>
       <c r="D41" t="n">
-        <v>4.395</v>
+        <v>1.861</v>
       </c>
       <c r="E41" t="n">
-        <v>7.711</v>
+        <v>3.583</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="G41" t="n">
-        <v>2.395</v>
+        <v>2.778</v>
       </c>
       <c r="H41" t="n">
-        <v>2.263</v>
+        <v>2.333</v>
       </c>
       <c r="I41" t="n">
-        <v>2.763</v>
+        <v>2.833</v>
       </c>
       <c r="J41" t="n">
-        <v>1.737</v>
+        <v>0.806</v>
       </c>
       <c r="K41" t="n">
-        <v>2.5</v>
+        <v>3.333</v>
       </c>
       <c r="L41" t="n">
-        <v>1.684</v>
+        <v>1.778</v>
       </c>
       <c r="M41" t="n">
-        <v>0.579</v>
+        <v>0.889</v>
       </c>
       <c r="N41" t="n">
-        <v>1.158</v>
+        <v>0.306</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.158</v>
+        <v>0.889</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.105</v>
+        <v>0.833</v>
       </c>
       <c r="R41" t="n">
-        <v>1.895</v>
+        <v>2.528</v>
       </c>
       <c r="S41" t="n">
-        <v>2.763</v>
+        <v>2.472</v>
       </c>
       <c r="T41" t="n">
-        <v>588</v>
+        <v>388</v>
       </c>
       <c r="U41" t="n">
-        <v>1.053</v>
+        <v>0.167</v>
       </c>
       <c r="V41" t="n">
-        <v>2.342</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.132</v>
+        <v>0.083</v>
       </c>
       <c r="X41" t="n">
-        <v>0.711</v>
+        <v>0.028</v>
       </c>
       <c r="Y41" t="n">
-        <v>5.263</v>
+        <v>3.556</v>
       </c>
       <c r="Z41" t="n">
-        <v>6.842</v>
+        <v>4.111</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.769</v>
+        <v>0.865</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.263</v>
+        <v>0.611</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.816</v>
+        <v>1.556</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.449</v>
+        <v>0.393</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.132</v>
+        <v>0.028</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.316</v>
+        <v>0.25</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.417</v>
+        <v>0.111</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.026</v>
+        <v>0.167</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.079</v>
+        <v>0.444</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.789</v>
+        <v>0.722</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.316</v>
+        <v>2.333</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.341</v>
+        <v>0.31</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>40:32</t>
+          <t>24:35</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>12.479</v>
+        <v>8.497</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.556</v>
+        <v>0.502</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.596</v>
+        <v>0.573</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.082</v>
+        <v>1.027</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.093</v>
+        <v>0.105</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.224</v>
+        <v>0.367</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.5</v>
+        <v>0.906</v>
       </c>
       <c r="AV41" t="n">
-        <v>8.727</v>
+        <v>7.156</v>
       </c>
       <c r="AW41" t="n">
-        <v>10.227</v>
+        <v>8.061999999999999</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.139</v>
+        <v>0.156</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.045</v>
+        <v>0.078</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="BA41" t="n">
-        <v>0.067</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#10 O. BRISSETT (Per Game)</t>
+          <t>#11 W. RAYMAN (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C42" t="n">
-        <v>8.722</v>
+        <v>3.105</v>
       </c>
       <c r="D42" t="n">
-        <v>1.861</v>
+        <v>0.342</v>
       </c>
       <c r="E42" t="n">
-        <v>3.583</v>
+        <v>0.947</v>
       </c>
       <c r="F42" t="n">
-        <v>0.889</v>
+        <v>0.5</v>
       </c>
       <c r="G42" t="n">
-        <v>2.778</v>
+        <v>1.316</v>
       </c>
       <c r="H42" t="n">
-        <v>2.333</v>
+        <v>0.921</v>
       </c>
       <c r="I42" t="n">
-        <v>2.833</v>
+        <v>1.395</v>
       </c>
       <c r="J42" t="n">
-        <v>0.806</v>
+        <v>0.263</v>
       </c>
       <c r="K42" t="n">
-        <v>3.333</v>
+        <v>1.211</v>
       </c>
       <c r="L42" t="n">
-        <v>1.778</v>
+        <v>0.868</v>
       </c>
       <c r="M42" t="n">
-        <v>0.889</v>
+        <v>0.263</v>
       </c>
       <c r="N42" t="n">
-        <v>0.306</v>
+        <v>0.342</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.889</v>
+        <v>0.184</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.833</v>
+        <v>0.158</v>
       </c>
       <c r="R42" t="n">
-        <v>2.528</v>
+        <v>2.289</v>
       </c>
       <c r="S42" t="n">
-        <v>2.472</v>
+        <v>1.605</v>
       </c>
       <c r="T42" t="n">
-        <v>388</v>
+        <v>125</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>2.028</v>
+        <v>0.053</v>
       </c>
       <c r="W42" t="n">
-        <v>0.611</v>
+        <v>0.079</v>
       </c>
       <c r="X42" t="n">
-        <v>0.444</v>
+        <v>0.026</v>
       </c>
       <c r="Y42" t="n">
-        <v>3.556</v>
+        <v>1.132</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.111</v>
+        <v>1.368</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.865</v>
+        <v>0.827</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.611</v>
+        <v>0.105</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.556</v>
+        <v>0.421</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.393</v>
+        <v>0.25</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.028</v>
+        <v>0.026</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.25</v>
+        <v>0.079</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.111</v>
+        <v>0.333</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.167</v>
+        <v>0.158</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.444</v>
+        <v>0.342</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.375</v>
+        <v>0.462</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.722</v>
+        <v>0.342</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.333</v>
+        <v>0.974</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.31</v>
+        <v>0.351</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>45:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>8.497</v>
+        <v>3.061</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.502</v>
+        <v>0.483</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.573</v>
+        <v>0.54</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.027</v>
+        <v>1.014</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.105</v>
+        <v>0.06</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.367</v>
+        <v>0.407</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.906</v>
+        <v>1.429</v>
       </c>
       <c r="AV42" t="n">
-        <v>7.156</v>
+        <v>12.286</v>
       </c>
       <c r="AW42" t="n">
-        <v>8.061999999999999</v>
+        <v>13.714</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.115</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.042</v>
+        <v>0.078</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.117</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.029</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#11 W. RAYMAN (Per Game)</t>
+          <t>#12 J. DIBARTOLOMEO (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C43" t="n">
-        <v>3.105</v>
+        <v>3.406</v>
       </c>
       <c r="D43" t="n">
-        <v>0.342</v>
+        <v>0.188</v>
       </c>
       <c r="E43" t="n">
-        <v>0.947</v>
+        <v>0.438</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>1.316</v>
+        <v>2.125</v>
       </c>
       <c r="H43" t="n">
-        <v>0.921</v>
+        <v>0.594</v>
       </c>
       <c r="I43" t="n">
-        <v>1.395</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>0.263</v>
+        <v>0.781</v>
       </c>
       <c r="K43" t="n">
-        <v>1.211</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>0.868</v>
+        <v>0.625</v>
       </c>
       <c r="M43" t="n">
-        <v>0.263</v>
+        <v>0.75</v>
       </c>
       <c r="N43" t="n">
-        <v>0.342</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0.184</v>
+        <v>0.281</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.158</v>
+        <v>0.281</v>
       </c>
       <c r="R43" t="n">
-        <v>2.289</v>
+        <v>1.688</v>
       </c>
       <c r="S43" t="n">
-        <v>1.605</v>
+        <v>0.906</v>
       </c>
       <c r="T43" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="U43" t="n">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0.579</v>
+        <v>0.062</v>
       </c>
       <c r="W43" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.132</v>
+        <v>0.656</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.368</v>
+        <v>0.75</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.827</v>
+        <v>0.875</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.105</v>
+        <v>0.062</v>
       </c>
       <c r="AC43" t="n">
-        <v>0.421</v>
+        <v>0.219</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="AE43" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="AO43" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>2.778</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>9.111000000000001</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>11.889</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="BA43" t="n">
         <v>0.026</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0.974</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>28:51</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>3.061</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.014</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>12.286</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>13.714</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#12 J. DIBARTOLOMEO (Per Game)</t>
+          <t>#13 T. GOLD (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C44" t="n">
-        <v>3.406</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0.438</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8120000000000001</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>2.125</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.594</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6879999999999999</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.781</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9379999999999999</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -7305,185 +7305,185 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.281</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.688</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.906</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0.656</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0.781</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.656</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>0.219</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.188</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.938</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.387</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>26:23</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>3.146</v>
+        <v>0</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.549</v>
+        <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.594</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.083</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.089</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>2.778</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>9.111000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>11.889</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.054</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#13 T. GOLD (Per Game)</t>
+          <t>#14 C. OMORUYI (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>9</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="T45" t="n">
         <v>3</v>
       </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>0.222</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>0.444</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -7543,44 +7543,44 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>01:47</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>0</v>
+        <v>0.431</v>
       </c>
       <c r="AP45" t="n">
         <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0</v>
+        <v>0.347</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>0.515</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="AT45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="n">
         <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX45" t="n">
-        <v>0</v>
+        <v>0.109</v>
       </c>
       <c r="AY45" t="n">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="BA45" t="n">
         <v>0</v>
@@ -7589,65 +7589,65 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#14 C. OMORUYI (Per Game)</t>
+          <t>#21 J. DOWTIN JR (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C46" t="n">
-        <v>0.222</v>
+        <v>4.935</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>0.222</v>
+        <v>2.323</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1.774</v>
       </c>
       <c r="H46" t="n">
-        <v>0.222</v>
+        <v>0.806</v>
       </c>
       <c r="I46" t="n">
-        <v>0.222</v>
+        <v>1.129</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1.484</v>
       </c>
       <c r="K46" t="n">
-        <v>0.111</v>
+        <v>0.516</v>
       </c>
       <c r="L46" t="n">
-        <v>0.444</v>
+        <v>0.129</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>0.355</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.111</v>
+        <v>0.548</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.111</v>
+        <v>0.484</v>
       </c>
       <c r="R46" t="n">
-        <v>0.222</v>
+        <v>0.774</v>
       </c>
       <c r="S46" t="n">
-        <v>0.111</v>
+        <v>1.032</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>141</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -7662,361 +7662,361 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.222</v>
+        <v>1.032</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.444</v>
+        <v>1.29</v>
       </c>
       <c r="AA46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.387</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="AG46" t="n">
         <v>0.5</v>
       </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>0.097</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>0.613</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.677</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>0.431</v>
+        <v>5.142</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.347</v>
+        <v>0.537</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.515</v>
+        <v>0.96</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.258</v>
+        <v>0.107</v>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>0.197</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>2.706</v>
       </c>
       <c r="AV46" t="n">
-        <v>2</v>
+        <v>7.471</v>
       </c>
       <c r="AW46" t="n">
-        <v>2</v>
+        <v>10.176</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.048</v>
+        <v>0.22</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.12</v>
+        <v>0.013</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.032</v>
+        <v>0.056</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#21 J. DOWTIN JR (Per Game)</t>
+          <t>#22 T. LEAF (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C47" t="n">
-        <v>4.935</v>
+        <v>9.125</v>
       </c>
       <c r="D47" t="n">
+        <v>3.417</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5.417</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.958</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="K47" t="n">
+        <v>2.708</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.958</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="T47" t="n">
+        <v>307</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>3.917</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>1.083</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AG47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="n">
-        <v>2.323</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1.774</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1.129</v>
-      </c>
-      <c r="J47" t="n">
-        <v>1.484</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.484</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="S47" t="n">
-        <v>1.032</v>
-      </c>
-      <c r="T47" t="n">
-        <v>141</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.032</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.387</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0.226</v>
-      </c>
-      <c r="AF47" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="AL47" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH47" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK47" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>1.677</v>
-      </c>
       <c r="AM47" t="n">
-        <v>0.365</v>
+        <v>0.417</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>5.142</v>
+        <v>7.237</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.504</v>
+        <v>0.63</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.537</v>
+        <v>0.673</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.96</v>
+        <v>1.261</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.107</v>
+        <v>0.063</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.197</v>
+        <v>0.282</v>
       </c>
       <c r="AU47" t="n">
-        <v>2.706</v>
+        <v>2.364</v>
       </c>
       <c r="AV47" t="n">
-        <v>7.471</v>
+        <v>12.909</v>
       </c>
       <c r="AW47" t="n">
-        <v>10.176</v>
+        <v>15.273</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.106</v>
+        <v>0.179</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.006</v>
+        <v>0.116</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.027</v>
+        <v>0.171</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.051</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#22 T. LEAF (Per Game)</t>
+          <t>#35 Z. HANKINS (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C48" t="n">
-        <v>9.125</v>
+        <v>3.286</v>
       </c>
       <c r="D48" t="n">
-        <v>3.417</v>
+        <v>1.429</v>
       </c>
       <c r="E48" t="n">
-        <v>5.417</v>
+        <v>1.857</v>
       </c>
       <c r="F48" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.929</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
         <v>0.5</v>
       </c>
-      <c r="H48" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1.958</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1.083</v>
-      </c>
-      <c r="K48" t="n">
-        <v>2.708</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1.958</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.417</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.542</v>
-      </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.458</v>
+        <v>0.357</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.458</v>
+        <v>0.357</v>
       </c>
       <c r="R48" t="n">
-        <v>1.542</v>
+        <v>1.429</v>
       </c>
       <c r="S48" t="n">
-        <v>1.542</v>
+        <v>0.571</v>
       </c>
       <c r="T48" t="n">
-        <v>307</v>
+        <v>54</v>
       </c>
       <c r="U48" t="n">
-        <v>0.792</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0.708</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>3.917</v>
+        <v>1.357</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.833</v>
+        <v>1.571</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.864</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.083</v>
+        <v>0.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.167</v>
+        <v>0.714</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.083</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
         <v>0</v>
@@ -8028,549 +8028,549 @@
         <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.208</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>40:46</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>7.237</v>
+        <v>2.497</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.63</v>
+        <v>0.769</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.673</v>
+        <v>0.768</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.261</v>
+        <v>1.316</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.063</v>
+        <v>0.143</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.282</v>
+        <v>0.231</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.364</v>
+        <v>0.8</v>
       </c>
       <c r="AV48" t="n">
-        <v>12.909</v>
+        <v>5.2</v>
       </c>
       <c r="AW48" t="n">
-        <v>15.273</v>
+        <v>6</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.08</v>
+        <v>0.153</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.052</v>
+        <v>0.136</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.076</v>
+        <v>0.112</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#35 Z. HANKINS (Per Game)</t>
+          <t>#45 T. BLATT (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C49" t="n">
-        <v>3.286</v>
+        <v>7.105</v>
       </c>
       <c r="D49" t="n">
-        <v>1.429</v>
+        <v>0.447</v>
       </c>
       <c r="E49" t="n">
-        <v>1.857</v>
+        <v>1.105</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1.842</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>4.789</v>
       </c>
       <c r="H49" t="n">
-        <v>0.429</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0.643</v>
+        <v>0.895</v>
       </c>
       <c r="J49" t="n">
-        <v>0.286</v>
+        <v>5.184</v>
       </c>
       <c r="K49" t="n">
-        <v>0.714</v>
+        <v>1.553</v>
       </c>
       <c r="L49" t="n">
-        <v>0.929</v>
+        <v>0.289</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="N49" t="n">
-        <v>0.5</v>
+        <v>0.053</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.357</v>
+        <v>2.263</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.357</v>
+        <v>2.158</v>
       </c>
       <c r="R49" t="n">
-        <v>1.429</v>
+        <v>0.737</v>
       </c>
       <c r="S49" t="n">
-        <v>0.571</v>
+        <v>1.395</v>
       </c>
       <c r="T49" t="n">
-        <v>54</v>
+        <v>344</v>
       </c>
       <c r="U49" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="AA49" t="n">
         <v>1</v>
       </c>
-      <c r="W49" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>1.571</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>0.864</v>
-      </c>
       <c r="AB49" t="n">
-        <v>0.5</v>
+        <v>0.211</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.714</v>
+        <v>0.526</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>0.553</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.381</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>0.079</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.816</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>4.711</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>2.497</v>
+        <v>8.552</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.769</v>
+        <v>0.545</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.768</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.316</v>
+        <v>0.831</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.143</v>
+        <v>0.265</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.231</v>
+        <v>0.116</v>
       </c>
       <c r="AU49" t="n">
-        <v>0.8</v>
+        <v>2.291</v>
       </c>
       <c r="AV49" t="n">
-        <v>5.2</v>
+        <v>2.605</v>
       </c>
       <c r="AW49" t="n">
-        <v>6</v>
+        <v>4.895</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.078</v>
+        <v>0.198</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.016</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.057</v>
+        <v>0.092</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.01</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#45 T. BLATT (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
         <v>38</v>
       </c>
       <c r="C50" t="n">
-        <v>7.105</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2.026</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2.105</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
         <v>0.447</v>
       </c>
-      <c r="E50" t="n">
-        <v>1.105</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1.842</v>
-      </c>
-      <c r="G50" t="n">
-        <v>4.789</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.6840000000000001</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="J50" t="n">
-        <v>5.184</v>
-      </c>
-      <c r="K50" t="n">
-        <v>1.553</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.263</v>
-      </c>
       <c r="Q50" t="n">
-        <v>2.158</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.737</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1.395</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0.947</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.842</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.368</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.711</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.711</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.526</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.553</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.381</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.816</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>4.711</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>41:07</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>8.552</v>
+        <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.831</v>
+        <v>0</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.265</v>
+        <v>0</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.116</v>
+        <v>0</v>
       </c>
       <c r="AU50" t="n">
-        <v>2.291</v>
+        <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>2.605</v>
+        <v>0</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.895</v>
+        <v>0</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.094</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.008</v>
+        <v>0</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="BA50" t="n">
-        <v>0.181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>38</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>90.13200000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>20.921</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>38.895</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>10.079</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>28.553</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>18.053</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>22.553</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>19.921</v>
       </c>
       <c r="K51" t="n">
-        <v>2.026</v>
+        <v>22.921</v>
       </c>
       <c r="L51" t="n">
-        <v>2.105</v>
+        <v>12.921</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>6.789</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>4.526</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
+        <v>12.263</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>11.263</v>
+      </c>
+      <c r="R51" t="n">
+        <v>19.579</v>
+      </c>
+      <c r="S51" t="n">
+        <v>21.947</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4042</v>
+      </c>
+      <c r="U51" t="n">
         <v>0.447</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>30.579</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>37.211</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>0.822</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>6.763</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>15.684</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>0.431</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.632</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>4.053</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.403</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>0.842</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1.763</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>9.237</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>26.789</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>0.345</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:58</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>0</v>
+        <v>89.634</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>0.534</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>0.582</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.006</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>0.137</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>1.624</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>7.124</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>0.131</v>
       </c>
       <c r="BA51" t="n">
         <v>0</v>
@@ -8579,495 +8579,165 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B52" t="n">
         <v>38</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>92.658</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>22.026</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>36.895</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>10.447</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>29.553</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>17.263</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>21.842</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>21.526</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>12.184</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>6.211</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.526</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>12.789</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>11.842</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>19.553</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>21.421</v>
       </c>
       <c r="T52" t="n">
-        <v>140</v>
+        <v>4261</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>0.447</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>29.974</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>34.947</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>0.858</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>7.974</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>15.974</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>0.499</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.342</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>3.237</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>0.415</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1.026</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>2.711</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>0.379</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>9.420999999999999</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>26.842</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:58</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>0.447</v>
+        <v>88.84699999999999</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>0.609</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.043</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>1.683</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>5.195</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>6.879</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>38</v>
-      </c>
-      <c r="C53" t="n">
-        <v>90.13200000000001</v>
-      </c>
-      <c r="D53" t="n">
-        <v>20.921</v>
-      </c>
-      <c r="E53" t="n">
-        <v>38.895</v>
-      </c>
-      <c r="F53" t="n">
-        <v>10.079</v>
-      </c>
-      <c r="G53" t="n">
-        <v>28.553</v>
-      </c>
-      <c r="H53" t="n">
-        <v>18.053</v>
-      </c>
-      <c r="I53" t="n">
-        <v>22.553</v>
-      </c>
-      <c r="J53" t="n">
-        <v>19.921</v>
-      </c>
-      <c r="K53" t="n">
-        <v>22.921</v>
-      </c>
-      <c r="L53" t="n">
-        <v>12.921</v>
-      </c>
-      <c r="M53" t="n">
-        <v>6.789</v>
-      </c>
-      <c r="N53" t="n">
-        <v>4.526</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>12.263</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>11.211</v>
-      </c>
-      <c r="R53" t="n">
-        <v>19.579</v>
-      </c>
-      <c r="S53" t="n">
-        <v>21.947</v>
-      </c>
-      <c r="T53" t="n">
-        <v>4042</v>
-      </c>
-      <c r="U53" t="n">
-        <v>11.132</v>
-      </c>
-      <c r="V53" t="n">
-        <v>13.868</v>
-      </c>
-      <c r="W53" t="n">
-        <v>8.683999999999999</v>
-      </c>
-      <c r="X53" t="n">
-        <v>5.105</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>30.579</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>37.211</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>6.763</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>15.684</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1.632</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>4.053</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0.842</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.763</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>9.237</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>26.789</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>201:58</t>
-        </is>
-      </c>
-      <c r="AO53" t="n">
-        <v>89.634</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>0.534</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0.582</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0.268</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>1.624</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>7.124</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="BA53" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>38</v>
-      </c>
-      <c r="C54" t="n">
-        <v>92.658</v>
-      </c>
-      <c r="D54" t="n">
-        <v>22.026</v>
-      </c>
-      <c r="E54" t="n">
-        <v>36.895</v>
-      </c>
-      <c r="F54" t="n">
-        <v>10.447</v>
-      </c>
-      <c r="G54" t="n">
-        <v>29.553</v>
-      </c>
-      <c r="H54" t="n">
-        <v>17.263</v>
-      </c>
-      <c r="I54" t="n">
-        <v>21.842</v>
-      </c>
-      <c r="J54" t="n">
-        <v>21.526</v>
-      </c>
-      <c r="K54" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="L54" t="n">
-        <v>12.184</v>
-      </c>
-      <c r="M54" t="n">
-        <v>6.211</v>
-      </c>
-      <c r="N54" t="n">
-        <v>4.526</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>12.789</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>11.842</v>
-      </c>
-      <c r="R54" t="n">
-        <v>19.553</v>
-      </c>
-      <c r="S54" t="n">
-        <v>21.421</v>
-      </c>
-      <c r="T54" t="n">
-        <v>4261</v>
-      </c>
-      <c r="U54" t="n">
-        <v>10.553</v>
-      </c>
-      <c r="V54" t="n">
-        <v>12.842</v>
-      </c>
-      <c r="W54" t="n">
-        <v>9.789</v>
-      </c>
-      <c r="X54" t="n">
-        <v>5.737</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>29.974</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>34.947</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0.858</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>7.974</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>15.974</v>
-      </c>
-      <c r="AD54" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>1.342</v>
-      </c>
-      <c r="AF54" t="n">
-        <v>3.237</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>1.026</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>2.711</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>9.420999999999999</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>26.842</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>201:58</t>
-        </is>
-      </c>
-      <c r="AO54" t="n">
-        <v>88.84699999999999</v>
-      </c>
-      <c r="AP54" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>1.043</v>
-      </c>
-      <c r="AS54" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AT54" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>1.683</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>5.195</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>6.879</v>
-      </c>
-      <c r="AX54" t="n">
-        <v>0.198</v>
-      </c>
-      <c r="AY54" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA54" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_MACCABI RAPYD TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_MACCABI RAPYD TEL AVIV.xlsx
@@ -671,13 +671,13 @@
         <v>0.2676550916894265</v>
       </c>
       <c r="J2" t="n">
-        <v>17</v>
+        <v>442</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>530</v>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="M2" t="n">
         <v>428</v>
@@ -752,13 +752,13 @@
         <v>1.058986175115207</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.03497942386831276</v>
+        <v>0.9094650205761317</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.03869653767820774</v>
+        <v>1.079429735234216</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>1.663414634146341</v>
       </c>
       <c r="AN2" t="n">
         <v>1.624463519313305</v>
@@ -801,13 +801,13 @@
         <v>0.2676550916894265</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4473684210526316</v>
+        <v>11.63157894736842</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>13.94736842105263</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5263157894736842</v>
+        <v>8.973684210526315</v>
       </c>
       <c r="M3" t="n">
         <v>11.26315789473684</v>
@@ -882,13 +882,13 @@
         <v>1.058986175115207</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.03497942386831276</v>
+        <v>0.9094650205761318</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.03869653767820774</v>
+        <v>1.079429735234216</v>
       </c>
       <c r="AM3" t="n">
-        <v>2</v>
+        <v>1.663414634146341</v>
       </c>
       <c r="AN3" t="n">
         <v>1.624463519313305</v>
@@ -931,13 +931,13 @@
         <v>0.2598019801980198</v>
       </c>
       <c r="J4" t="n">
-        <v>15</v>
+        <v>411</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="L4" t="n">
-        <v>17</v>
+        <v>382</v>
       </c>
       <c r="M4" t="n">
         <v>450</v>
@@ -1012,13 +1012,13 @@
         <v>1.060552092609083</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.03218884120171674</v>
+        <v>0.8819742489270386</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03455723542116631</v>
+        <v>1.079913606911447</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.125</v>
+        <v>1.682819383259912</v>
       </c>
       <c r="AN4" t="n">
         <v>1.683127572016461</v>
@@ -1061,13 +1061,13 @@
         <v>0.2598019801980198</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3947368421052632</v>
+        <v>10.81578947368421</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4210526315789473</v>
+        <v>13.1578947368421</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4473684210526316</v>
+        <v>10.05263157894737</v>
       </c>
       <c r="M5" t="n">
         <v>11.8421052631579</v>
@@ -1142,13 +1142,13 @@
         <v>1.060552092609083</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.03218884120171674</v>
+        <v>0.8819742489270386</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.0345572354211663</v>
+        <v>1.079913606911447</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.125</v>
+        <v>1.682819383259912</v>
       </c>
       <c r="AN5" t="n">
         <v>1.683127572016461</v>
@@ -1486,16 +1486,16 @@
         <v>207</v>
       </c>
       <c r="U8" t="n">
+        <v>44</v>
+      </c>
+      <c r="V8" t="n">
         <v>5</v>
       </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
         <v>46</v>
@@ -1651,16 +1651,16 @@
         <v>603</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y9" t="n">
         <v>193</v>
@@ -1816,16 +1816,16 @@
         <v>338</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="W10" t="n">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="Y10" t="n">
         <v>98</v>
@@ -1981,16 +1981,16 @@
         <v>243</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="n">
         <v>112</v>
@@ -2146,16 +2146,16 @@
         <v>58</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y12" t="n">
         <v>20</v>
@@ -2806,16 +2806,16 @@
         <v>380</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="Y16" t="n">
         <v>127</v>
@@ -2971,16 +2971,16 @@
         <v>588</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="V17" t="n">
-        <v>2</v>
+        <v>91</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="Y17" t="n">
         <v>200</v>
@@ -3136,16 +3136,16 @@
         <v>388</v>
       </c>
       <c r="U18" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
         <v>128</v>
@@ -3301,16 +3301,16 @@
         <v>125</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="W19" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="n">
         <v>43</v>
@@ -3466,16 +3466,16 @@
         <v>121</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="V20" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
@@ -3961,16 +3961,16 @@
         <v>141</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="n">
         <v>32</v>
@@ -4126,16 +4126,16 @@
         <v>307</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V24" t="n">
-        <v>6</v>
+        <v>64</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y24" t="n">
         <v>94</v>
@@ -4291,10 +4291,10 @@
         <v>54</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
@@ -4456,16 +4456,16 @@
         <v>344</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="W26" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="Y26" t="n">
         <v>27</v>
@@ -4786,16 +4786,16 @@
         <v>4042</v>
       </c>
       <c r="U28" t="n">
-        <v>17</v>
+        <v>442</v>
       </c>
       <c r="V28" t="n">
-        <v>19</v>
+        <v>530</v>
       </c>
       <c r="W28" t="n">
-        <v>20</v>
+        <v>341</v>
       </c>
       <c r="X28" t="n">
-        <v>10</v>
+        <v>205</v>
       </c>
       <c r="Y28" t="n">
         <v>1162</v>
@@ -4951,16 +4951,16 @@
         <v>4261</v>
       </c>
       <c r="U29" t="n">
-        <v>15</v>
+        <v>411</v>
       </c>
       <c r="V29" t="n">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="W29" t="n">
-        <v>17</v>
+        <v>382</v>
       </c>
       <c r="X29" t="n">
-        <v>8</v>
+        <v>227</v>
       </c>
       <c r="Y29" t="n">
         <v>1139</v>
@@ -5175,16 +5175,16 @@
         <v>207</v>
       </c>
       <c r="U31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V31" t="n">
         <v>0.312</v>
       </c>
-      <c r="V31" t="n">
-        <v>0.188</v>
-      </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="Y31" t="n">
         <v>2.875</v>
@@ -5340,16 +5340,16 @@
         <v>603</v>
       </c>
       <c r="U32" t="n">
-        <v>0.056</v>
+        <v>1.611</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.806</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Y32" t="n">
         <v>5.361</v>
@@ -5505,16 +5505,16 @@
         <v>338</v>
       </c>
       <c r="U33" t="n">
-        <v>0.108</v>
+        <v>1.784</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.676</v>
       </c>
       <c r="W33" t="n">
-        <v>0.135</v>
+        <v>1.297</v>
       </c>
       <c r="X33" t="n">
-        <v>0.054</v>
+        <v>0.757</v>
       </c>
       <c r="Y33" t="n">
         <v>2.649</v>
@@ -5670,16 +5670,16 @@
         <v>243</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="V34" t="n">
-        <v>0.053</v>
+        <v>1.184</v>
       </c>
       <c r="W34" t="n">
-        <v>0.053</v>
+        <v>0.711</v>
       </c>
       <c r="X34" t="n">
-        <v>0.053</v>
+        <v>0.474</v>
       </c>
       <c r="Y34" t="n">
         <v>2.947</v>
@@ -6000,16 +6000,16 @@
         <v>58</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.174</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.348</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>0.391</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>0.304</v>
       </c>
       <c r="Y36" t="n">
         <v>0.87</v>
@@ -6495,16 +6495,16 @@
         <v>380</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.862</v>
       </c>
       <c r="V39" t="n">
-        <v>0.06900000000000001</v>
+        <v>1.276</v>
       </c>
       <c r="W39" t="n">
-        <v>0.06900000000000001</v>
+        <v>2.345</v>
       </c>
       <c r="X39" t="n">
-        <v>0.06900000000000001</v>
+        <v>1.207</v>
       </c>
       <c r="Y39" t="n">
         <v>4.379</v>
@@ -6660,16 +6660,16 @@
         <v>588</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.105</v>
       </c>
       <c r="V40" t="n">
-        <v>0.053</v>
+        <v>2.395</v>
       </c>
       <c r="W40" t="n">
-        <v>0.053</v>
+        <v>1.132</v>
       </c>
       <c r="X40" t="n">
-        <v>0.026</v>
+        <v>0.711</v>
       </c>
       <c r="Y40" t="n">
         <v>5.263</v>
@@ -6825,16 +6825,16 @@
         <v>388</v>
       </c>
       <c r="U41" t="n">
-        <v>0.167</v>
+        <v>1.056</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.972</v>
       </c>
       <c r="W41" t="n">
-        <v>0.083</v>
+        <v>0.722</v>
       </c>
       <c r="X41" t="n">
-        <v>0.028</v>
+        <v>0.556</v>
       </c>
       <c r="Y41" t="n">
         <v>3.556</v>
@@ -6990,16 +6990,16 @@
         <v>125</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="V42" t="n">
-        <v>0.053</v>
+        <v>0.605</v>
       </c>
       <c r="W42" t="n">
-        <v>0.079</v>
+        <v>0.316</v>
       </c>
       <c r="X42" t="n">
-        <v>0.026</v>
+        <v>0.211</v>
       </c>
       <c r="Y42" t="n">
         <v>1.132</v>
@@ -7155,16 +7155,16 @@
         <v>121</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>0.656</v>
       </c>
       <c r="V43" t="n">
-        <v>0.062</v>
+        <v>0.781</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="Y43" t="n">
         <v>0.656</v>
@@ -7650,16 +7650,16 @@
         <v>141</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.161</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>0.516</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="Y46" t="n">
         <v>1.032</v>
@@ -7815,16 +7815,16 @@
         <v>307</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>0.792</v>
       </c>
       <c r="V47" t="n">
-        <v>0.25</v>
+        <v>2.667</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.708</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="Y47" t="n">
         <v>3.917</v>
@@ -7980,10 +7980,10 @@
         <v>54</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.857</v>
       </c>
       <c r="W48" t="n">
         <v>0</v>
@@ -8145,16 +8145,16 @@
         <v>344</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.947</v>
       </c>
       <c r="W49" t="n">
-        <v>0.079</v>
+        <v>0.842</v>
       </c>
       <c r="X49" t="n">
-        <v>0.026</v>
+        <v>0.368</v>
       </c>
       <c r="Y49" t="n">
         <v>0.711</v>
@@ -8475,16 +8475,16 @@
         <v>4042</v>
       </c>
       <c r="U51" t="n">
-        <v>0.447</v>
+        <v>11.632</v>
       </c>
       <c r="V51" t="n">
-        <v>0.5</v>
+        <v>13.947</v>
       </c>
       <c r="W51" t="n">
-        <v>0.526</v>
+        <v>8.974</v>
       </c>
       <c r="X51" t="n">
-        <v>0.263</v>
+        <v>5.395</v>
       </c>
       <c r="Y51" t="n">
         <v>30.579</v>
@@ -8640,16 +8640,16 @@
         <v>4261</v>
       </c>
       <c r="U52" t="n">
-        <v>0.395</v>
+        <v>10.816</v>
       </c>
       <c r="V52" t="n">
-        <v>0.421</v>
+        <v>13.158</v>
       </c>
       <c r="W52" t="n">
-        <v>0.447</v>
+        <v>10.053</v>
       </c>
       <c r="X52" t="n">
-        <v>0.211</v>
+        <v>5.974</v>
       </c>
       <c r="Y52" t="n">
         <v>29.974</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_MACCABI RAPYD TEL AVIV.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_MACCABI RAPYD TEL AVIV.xlsx
@@ -683,13 +683,13 @@
         <v>428</v>
       </c>
       <c r="N2" t="n">
-        <v>1162</v>
+        <v>476</v>
       </c>
       <c r="O2" t="n">
-        <v>1414</v>
+        <v>728</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5516972298088177</v>
+        <v>0.2840421381193913</v>
       </c>
       <c r="Q2" t="n">
         <v>257</v>
@@ -710,25 +710,25 @@
         <v>0.06008583690987124</v>
       </c>
       <c r="W2" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="X2" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.02614124073351541</v>
+        <v>0.03589543503706594</v>
       </c>
       <c r="Z2" t="n">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="AA2" t="n">
-        <v>1018</v>
+        <v>993</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3971907920405774</v>
+        <v>0.3874365977370269</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8217821782178217</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4312080536912752</v>
@@ -737,13 +737,13 @@
         <v>0.4025974025974026</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4776119402985075</v>
+        <v>0.4456521739130435</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3447937131630648</v>
+        <v>0.3444108761329305</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.643564356435643</v>
+        <v>1.307692307692308</v>
       </c>
       <c r="AI2" t="n">
         <v>0.8051948051948052</v>
@@ -813,13 +813,13 @@
         <v>11.26315789473684</v>
       </c>
       <c r="N3" t="n">
-        <v>30.57894736842105</v>
+        <v>12.52631578947368</v>
       </c>
       <c r="O3" t="n">
-        <v>37.21052631578947</v>
+        <v>19.15789473684211</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5516972298088177</v>
+        <v>0.2840421381193914</v>
       </c>
       <c r="Q3" t="n">
         <v>6.763157894736842</v>
@@ -840,25 +840,25 @@
         <v>0.06008583690987124</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8421052631578947</v>
+        <v>1.078947368421053</v>
       </c>
       <c r="X3" t="n">
-        <v>1.763157894736842</v>
+        <v>2.421052631578947</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02614124073351541</v>
+        <v>0.03589543503706594</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.236842105263158</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.78947368421053</v>
+        <v>26.13157894736842</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3971907920405775</v>
+        <v>0.3874365977370269</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8217821782178217</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4312080536912752</v>
@@ -867,13 +867,13 @@
         <v>0.4025974025974026</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4776119402985075</v>
+        <v>0.4456521739130435</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3447937131630648</v>
+        <v>0.3444108761329305</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.643564356435643</v>
+        <v>1.307692307692308</v>
       </c>
       <c r="AI3" t="n">
         <v>0.8051948051948052</v>
@@ -943,13 +943,13 @@
         <v>450</v>
       </c>
       <c r="N4" t="n">
-        <v>1139</v>
+        <v>483</v>
       </c>
       <c r="O4" t="n">
-        <v>1328</v>
+        <v>672</v>
       </c>
       <c r="P4" t="n">
-        <v>0.525940594059406</v>
+        <v>0.2661386138613862</v>
       </c>
       <c r="Q4" t="n">
         <v>303</v>
@@ -970,25 +970,25 @@
         <v>0.04871287128712871</v>
       </c>
       <c r="W4" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="X4" t="n">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04079207920792079</v>
+        <v>0.05782178217821782</v>
       </c>
       <c r="Z4" t="n">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="AA4" t="n">
-        <v>1020</v>
+        <v>977</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.403960396039604</v>
+        <v>0.3869306930693069</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.8576807228915663</v>
+        <v>0.71875</v>
       </c>
       <c r="AD4" t="n">
         <v>0.499176276771005</v>
@@ -997,13 +997,13 @@
         <v>0.4146341463414634</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3786407766990291</v>
+        <v>0.3972602739726027</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3509803921568627</v>
+        <v>0.3469805527123849</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.715361445783133</v>
+        <v>1.4375</v>
       </c>
       <c r="AI4" t="n">
         <v>0.8292682926829268</v>
@@ -1073,13 +1073,13 @@
         <v>11.8421052631579</v>
       </c>
       <c r="N5" t="n">
-        <v>29.97368421052632</v>
+        <v>12.71052631578947</v>
       </c>
       <c r="O5" t="n">
-        <v>34.94736842105263</v>
+        <v>17.68421052631579</v>
       </c>
       <c r="P5" t="n">
-        <v>0.525940594059406</v>
+        <v>0.2661386138613862</v>
       </c>
       <c r="Q5" t="n">
         <v>7.973684210526316</v>
@@ -1100,25 +1100,25 @@
         <v>0.04871287128712871</v>
       </c>
       <c r="W5" t="n">
-        <v>1.026315789473684</v>
+        <v>1.526315789473684</v>
       </c>
       <c r="X5" t="n">
-        <v>2.710526315789474</v>
+        <v>3.842105263157895</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04079207920792079</v>
+        <v>0.05782178217821782</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.421052631578947</v>
+        <v>8.921052631578947</v>
       </c>
       <c r="AA5" t="n">
-        <v>26.84210526315789</v>
+        <v>25.71052631578947</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4039603960396039</v>
+        <v>0.3869306930693069</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.8576807228915663</v>
+        <v>0.71875</v>
       </c>
       <c r="AD5" t="n">
         <v>0.499176276771005</v>
@@ -1127,13 +1127,13 @@
         <v>0.4146341463414634</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3786407766990291</v>
+        <v>0.3972602739726028</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3509803921568627</v>
+        <v>0.3469805527123849</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.715361445783133</v>
+        <v>1.4375</v>
       </c>
       <c r="AI5" t="n">
         <v>0.8292682926829268</v>
@@ -1498,13 +1498,13 @@
         <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="Z8" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.92</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB8" t="n">
         <v>20</v>
@@ -1528,19 +1528,19 @@
         <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AK8" t="n">
         <v>21</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.323</v>
+        <v>0.328</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>18</v>
       </c>
       <c r="Y9" t="n">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="Z9" t="n">
-        <v>238</v>
+        <v>143</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AB9" t="n">
         <v>28</v>
@@ -1693,19 +1693,19 @@
         <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="AK9" t="n">
         <v>11</v>
       </c>
       <c r="AL9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.275</v>
+        <v>0.289</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1828,13 +1828,13 @@
         <v>28</v>
       </c>
       <c r="Y10" t="n">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="Z10" t="n">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.772</v>
+        <v>0.651</v>
       </c>
       <c r="AB10" t="n">
         <v>29</v>
@@ -1858,19 +1858,19 @@
         <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK10" t="n">
         <v>43</v>
       </c>
       <c r="AL10" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.307</v>
+        <v>0.309</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         <v>18</v>
       </c>
       <c r="Y11" t="n">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="Z11" t="n">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.875</v>
+        <v>0.652</v>
       </c>
       <c r="AB11" t="n">
         <v>19</v>
@@ -2020,22 +2020,22 @@
         <v>0.333</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.407</v>
+        <v>0.418</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
@@ -2158,13 +2158,13 @@
         <v>7</v>
       </c>
       <c r="Y12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="AB12" t="n">
         <v>6</v>
@@ -2818,13 +2818,13 @@
         <v>35</v>
       </c>
       <c r="Y16" t="n">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="Z16" t="n">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.83</v>
+        <v>0.536</v>
       </c>
       <c r="AB16" t="n">
         <v>20</v>
@@ -2845,22 +2845,22 @@
         <v>0.414</v>
       </c>
       <c r="AH16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AK16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AL16" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         <v>27</v>
       </c>
       <c r="Y17" t="n">
-        <v>200</v>
+        <v>114</v>
       </c>
       <c r="Z17" t="n">
-        <v>260</v>
+        <v>174</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.769</v>
+        <v>0.655</v>
       </c>
       <c r="AB17" t="n">
         <v>48</v>
@@ -3148,13 +3148,13 @@
         <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="Z18" t="n">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.865</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB18" t="n">
         <v>22</v>
@@ -3175,22 +3175,22 @@
         <v>0.111</v>
       </c>
       <c r="AH18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
@@ -3313,13 +3313,13 @@
         <v>8</v>
       </c>
       <c r="Y19" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.827</v>
+        <v>0.471</v>
       </c>
       <c r="AB19" t="n">
         <v>4</v>
@@ -3340,22 +3340,22 @@
         <v>0.333</v>
       </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI19" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.462</v>
+        <v>0.471</v>
       </c>
       <c r="AK19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL19" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.351</v>
+        <v>0.333</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
@@ -3478,13 +3478,13 @@
         <v>7</v>
       </c>
       <c r="Y20" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.875</v>
+        <v>0.4</v>
       </c>
       <c r="AB20" t="n">
         <v>2</v>
@@ -3508,19 +3508,19 @@
         <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK20" t="n">
         <v>24</v>
       </c>
       <c r="AL20" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.387</v>
+        <v>0.4</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -3808,13 +3808,13 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2</v>
       </c>
-      <c r="Z22" t="n">
-        <v>4</v>
-      </c>
       <c r="AA22" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3973,13 +3973,13 @@
         <v>2</v>
       </c>
       <c r="Y23" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="Z23" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.8</v>
+        <v>0.467</v>
       </c>
       <c r="AB23" t="n">
         <v>17</v>
@@ -4000,22 +4000,22 @@
         <v>0.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="AK23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL23" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.365</v>
+        <v>0.354</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4138,13 +4138,13 @@
         <v>9</v>
       </c>
       <c r="Y24" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="Z24" t="n">
-        <v>116</v>
+        <v>76</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="AB24" t="n">
         <v>26</v>
@@ -4303,13 +4303,13 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.864</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AB25" t="n">
         <v>7</v>
@@ -4468,10 +4468,10 @@
         <v>14</v>
       </c>
       <c r="Y26" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
         <v>1</v>
@@ -4495,22 +4495,22 @@
         <v>0.381</v>
       </c>
       <c r="AH26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AL26" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.385</v>
+        <v>0.382</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
@@ -4798,13 +4798,13 @@
         <v>205</v>
       </c>
       <c r="Y28" t="n">
-        <v>1162</v>
+        <v>476</v>
       </c>
       <c r="Z28" t="n">
-        <v>1414</v>
+        <v>728</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.822</v>
+        <v>0.654</v>
       </c>
       <c r="AB28" t="n">
         <v>257</v>
@@ -4825,22 +4825,22 @@
         <v>0.403</v>
       </c>
       <c r="AH28" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="AI28" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.478</v>
+        <v>0.446</v>
       </c>
       <c r="AK28" t="n">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="AL28" t="n">
-        <v>1018</v>
+        <v>993</v>
       </c>
       <c r="AM28" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
@@ -4963,13 +4963,13 @@
         <v>227</v>
       </c>
       <c r="Y29" t="n">
-        <v>1139</v>
+        <v>483</v>
       </c>
       <c r="Z29" t="n">
-        <v>1328</v>
+        <v>672</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.858</v>
+        <v>0.719</v>
       </c>
       <c r="AB29" t="n">
         <v>303</v>
@@ -4990,22 +4990,22 @@
         <v>0.415</v>
       </c>
       <c r="AH29" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="AI29" t="n">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.379</v>
+        <v>0.397</v>
       </c>
       <c r="AK29" t="n">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="AL29" t="n">
-        <v>1020</v>
+        <v>977</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5187,13 +5187,13 @@
         <v>0.75</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.875</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.125</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.92</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB31" t="n">
         <v>1.25</v>
@@ -5217,19 +5217,19 @@
         <v>0.125</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.375</v>
+        <v>0.438</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AK31" t="n">
         <v>1.312</v>
       </c>
       <c r="AL31" t="n">
-        <v>4.062</v>
+        <v>4</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.323</v>
+        <v>0.328</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
         <v>0.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>5.361</v>
+        <v>2.722</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.611</v>
+        <v>3.972</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AB32" t="n">
         <v>0.778</v>
@@ -5382,19 +5382,19 @@
         <v>0.083</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.167</v>
+        <v>0.222</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.5</v>
+        <v>0.375</v>
       </c>
       <c r="AK32" t="n">
         <v>0.306</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.111</v>
+        <v>1.056</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.275</v>
+        <v>0.289</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>0.757</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.649</v>
+        <v>1.459</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.432</v>
+        <v>2.243</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.772</v>
+        <v>0.651</v>
       </c>
       <c r="AB33" t="n">
         <v>0.784</v>
@@ -5547,19 +5547,19 @@
         <v>0.027</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.081</v>
+        <v>0.108</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK33" t="n">
         <v>1.162</v>
       </c>
       <c r="AL33" t="n">
-        <v>3.784</v>
+        <v>3.757</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.307</v>
+        <v>0.309</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -5682,13 +5682,13 @@
         <v>0.474</v>
       </c>
       <c r="Y34" t="n">
-        <v>2.947</v>
+        <v>0.789</v>
       </c>
       <c r="Z34" t="n">
-        <v>3.368</v>
+        <v>1.211</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.875</v>
+        <v>0.652</v>
       </c>
       <c r="AB34" t="n">
         <v>0.5</v>
@@ -5709,22 +5709,22 @@
         <v>0.333</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.026</v>
+        <v>0.132</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.632</v>
+        <v>0.605</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.553</v>
+        <v>1.447</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.407</v>
+        <v>0.418</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
@@ -6012,13 +6012,13 @@
         <v>0.304</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.87</v>
+        <v>0.522</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.087</v>
+        <v>0.739</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.8</v>
+        <v>0.706</v>
       </c>
       <c r="AB36" t="n">
         <v>0.261</v>
@@ -6507,13 +6507,13 @@
         <v>1.207</v>
       </c>
       <c r="Y39" t="n">
-        <v>4.379</v>
+        <v>1.034</v>
       </c>
       <c r="Z39" t="n">
-        <v>5.276</v>
+        <v>1.931</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.83</v>
+        <v>0.536</v>
       </c>
       <c r="AB39" t="n">
         <v>0.6899999999999999</v>
@@ -6534,22 +6534,22 @@
         <v>0.414</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.138</v>
+        <v>0.172</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.138</v>
+        <v>0.207</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AK39" t="n">
-        <v>2.207</v>
+        <v>2.172</v>
       </c>
       <c r="AL39" t="n">
-        <v>6.552</v>
+        <v>6.483</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
@@ -6672,13 +6672,13 @@
         <v>0.711</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.263</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="n">
-        <v>6.842</v>
+        <v>4.579</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.769</v>
+        <v>0.655</v>
       </c>
       <c r="AB40" t="n">
         <v>1.263</v>
@@ -6837,13 +6837,13 @@
         <v>0.556</v>
       </c>
       <c r="Y41" t="n">
-        <v>3.556</v>
+        <v>1.222</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.111</v>
+        <v>1.778</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.865</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AB41" t="n">
         <v>0.611</v>
@@ -6864,22 +6864,22 @@
         <v>0.111</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.167</v>
+        <v>0.222</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.444</v>
+        <v>0.556</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.375</v>
+        <v>0.4</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.722</v>
+        <v>0.667</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.333</v>
+        <v>2.222</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
@@ -7002,13 +7002,13 @@
         <v>0.211</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.132</v>
+        <v>0.211</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.368</v>
+        <v>0.447</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.827</v>
+        <v>0.471</v>
       </c>
       <c r="AB42" t="n">
         <v>0.105</v>
@@ -7029,22 +7029,22 @@
         <v>0.333</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.158</v>
+        <v>0.211</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.342</v>
+        <v>0.447</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.462</v>
+        <v>0.471</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.342</v>
+        <v>0.289</v>
       </c>
       <c r="AL42" t="n">
-        <v>0.974</v>
+        <v>0.868</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.351</v>
+        <v>0.333</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
@@ -7167,13 +7167,13 @@
         <v>0.219</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.656</v>
+        <v>0.062</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.75</v>
+        <v>0.156</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.875</v>
+        <v>0.4</v>
       </c>
       <c r="AB43" t="n">
         <v>0.062</v>
@@ -7197,19 +7197,19 @@
         <v>0.062</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.188</v>
+        <v>0.25</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK43" t="n">
         <v>0.75</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.938</v>
+        <v>1.875</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.387</v>
+        <v>0.4</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
@@ -7497,13 +7497,13 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
         <v>0.222</v>
       </c>
-      <c r="Z45" t="n">
-        <v>0.444</v>
-      </c>
       <c r="AA45" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -7662,13 +7662,13 @@
         <v>0.065</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.032</v>
+        <v>0.226</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.29</v>
+        <v>0.484</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.8</v>
+        <v>0.467</v>
       </c>
       <c r="AB46" t="n">
         <v>0.548</v>
@@ -7689,22 +7689,22 @@
         <v>0.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.097</v>
+        <v>0.161</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.097</v>
+        <v>0.226</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.613</v>
+        <v>0.548</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.677</v>
+        <v>1.548</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.365</v>
+        <v>0.354</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
@@ -7827,13 +7827,13 @@
         <v>0.375</v>
       </c>
       <c r="Y47" t="n">
-        <v>3.917</v>
+        <v>2.25</v>
       </c>
       <c r="Z47" t="n">
-        <v>4.833</v>
+        <v>3.167</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.711</v>
       </c>
       <c r="AB47" t="n">
         <v>1.083</v>
@@ -7992,13 +7992,13 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.357</v>
+        <v>0.929</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.571</v>
+        <v>1.143</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.864</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="AB48" t="n">
         <v>0.5</v>
@@ -8157,10 +8157,10 @@
         <v>0.368</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.711</v>
+        <v>0.026</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.711</v>
+        <v>0.026</v>
       </c>
       <c r="AA49" t="n">
         <v>1</v>
@@ -8184,22 +8184,22 @@
         <v>0.381</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.026</v>
+        <v>0.053</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.079</v>
+        <v>0.105</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.816</v>
+        <v>1.789</v>
       </c>
       <c r="AL49" t="n">
-        <v>4.711</v>
+        <v>4.684</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.385</v>
+        <v>0.382</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
@@ -8487,13 +8487,13 @@
         <v>5.395</v>
       </c>
       <c r="Y51" t="n">
-        <v>30.579</v>
+        <v>12.526</v>
       </c>
       <c r="Z51" t="n">
-        <v>37.211</v>
+        <v>19.158</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.822</v>
+        <v>0.654</v>
       </c>
       <c r="AB51" t="n">
         <v>6.763</v>
@@ -8514,22 +8514,22 @@
         <v>0.403</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.842</v>
+        <v>1.079</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.763</v>
+        <v>2.421</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.478</v>
+        <v>0.446</v>
       </c>
       <c r="AK51" t="n">
-        <v>9.237</v>
+        <v>9</v>
       </c>
       <c r="AL51" t="n">
-        <v>26.789</v>
+        <v>26.132</v>
       </c>
       <c r="AM51" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
@@ -8652,13 +8652,13 @@
         <v>5.974</v>
       </c>
       <c r="Y52" t="n">
-        <v>29.974</v>
+        <v>12.711</v>
       </c>
       <c r="Z52" t="n">
-        <v>34.947</v>
+        <v>17.684</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.858</v>
+        <v>0.719</v>
       </c>
       <c r="AB52" t="n">
         <v>7.974</v>
@@ -8679,22 +8679,22 @@
         <v>0.415</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.026</v>
+        <v>1.526</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.711</v>
+        <v>3.842</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.379</v>
+        <v>0.397</v>
       </c>
       <c r="AK52" t="n">
-        <v>9.420999999999999</v>
+        <v>8.920999999999999</v>
       </c>
       <c r="AL52" t="n">
-        <v>26.842</v>
+        <v>25.711</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.351</v>
+        <v>0.347</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
